--- a/StructureDefinition-openelis-shipment-box.xlsx
+++ b/StructureDefinition-openelis-shipment-box.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="434">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T02:24:20+00:00</t>
+    <t>2026-10-12T15:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1111,6 +1111,10 @@
   </si>
   <si>
     <t>Number of items in the box, as {specimens} (UCUM).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>count of BoxSampleItem</t>
@@ -6398,16 +6402,16 @@
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>103</v>
+        <v>351</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6418,10 +6422,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6533,10 +6537,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6650,10 +6654,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6676,19 +6680,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6737,7 +6741,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6758,10 +6762,10 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -6769,10 +6773,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6798,20 +6802,20 @@
         <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R44" t="s" s="2">
         <v>79</v>
@@ -6835,10 +6839,10 @@
         <v>240</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
@@ -6856,7 +6860,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6877,10 +6881,10 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -6888,10 +6892,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6917,14 +6921,14 @@
         <v>223</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -6973,7 +6977,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6994,10 +6998,10 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7005,10 +7009,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7034,14 +7038,14 @@
         <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7051,7 +7055,7 @@
         <v>79</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>79</v>
@@ -7090,7 +7094,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7099,7 +7103,7 @@
         <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>103</v>
@@ -7111,10 +7115,10 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7122,10 +7126,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7151,16 +7155,16 @@
         <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7170,7 +7174,7 @@
         <v>79</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>79</v>
@@ -7209,7 +7213,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7230,10 +7234,10 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7241,10 +7245,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7270,13 +7274,13 @@
         <v>247</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7302,13 +7306,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7326,7 +7330,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7358,10 +7362,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7384,16 +7388,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7443,7 +7447,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7458,27 +7462,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>310</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7501,13 +7505,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7558,7 +7562,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7573,13 +7577,13 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>79</v>
@@ -7590,10 +7594,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7616,16 +7620,16 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7675,7 +7679,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7690,13 +7694,13 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>79</v>
@@ -7707,10 +7711,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7733,16 +7737,16 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7792,7 +7796,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7813,7 +7817,7 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>

--- a/StructureDefinition-openelis-shipment-box.xlsx
+++ b/StructureDefinition-openelis-shipment-box.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:07:11+00:00</t>
+    <t>2026-10-12T15:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-shipment-box.xlsx
+++ b/StructureDefinition-openelis-shipment-box.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:22:52+00:00</t>
+    <t>2026-10-14T21:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
